--- a/seo_forms/029_website_redesign_seo_checklist_form--seo_forms.xlsx
+++ b/seo_forms/029_website_redesign_seo_checklist_form--seo_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -780,8 +780,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -809,12 +809,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'none',_'label':_'none',_'value':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'none', 'label': 'none', 'value': 'none'}</t>
+          <t>none</t>
         </is>
       </c>
     </row>
@@ -826,12 +826,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_'minor',_'label':_'minor',_'value':_'minor'}</t>
+          <t>minor</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 'minor', 'label': 'minor', 'value': 'minor'}</t>
+          <t>minor</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_7,_'name':_'major',_'label':_'major',_'value':_'major'}</t>
+          <t>major</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 7, 'name': 'major', 'label': 'major', 'value': 'major'}</t>
+          <t>major</t>
         </is>
       </c>
     </row>
@@ -860,12 +860,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_8,_'name':_'critical',_'label':_'critical',_'value':_'critical'}</t>
+          <t>critical</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 8, 'name': 'critical', 'label': 'critical', 'value': 'critical'}</t>
+          <t>critical</t>
         </is>
       </c>
     </row>
@@ -877,12 +877,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_11,_'name':_'planning',_'label':_'planning',_'value':_'planning'}</t>
+          <t>planning</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 11, 'name': 'planning', 'label': 'planning', 'value': 'planning'}</t>
+          <t>planning</t>
         </is>
       </c>
     </row>
@@ -894,12 +894,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_12,_'name':_'design',_'label':_'design',_'value':_'design'}</t>
+          <t>design</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 12, 'name': 'design', 'label': 'design', 'value': 'design'}</t>
+          <t>design</t>
         </is>
       </c>
     </row>
@@ -911,12 +911,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_13,_'name':_'development',_'label':_'development',_'value':_'development'}</t>
+          <t>development</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 13, 'name': 'development', 'label': 'development', 'value': 'development'}</t>
+          <t>development</t>
         </is>
       </c>
     </row>
@@ -928,12 +928,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_14,_'name':_'launch',_'label':_'launch',_'value':_'launch'}</t>
+          <t>launch</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 14, 'name': 'launch', 'label': 'launch', 'value': 'launch'}</t>
+          <t>launch</t>
         </is>
       </c>
     </row>
@@ -945,12 +945,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_15,_'name':_'post_launch',_'label':_'post_launch',_'value':_'post_launch'}</t>
+          <t>post_launch</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 15, 'name': 'post_launch', 'label': 'post_launch', 'value': 'post_launch'}</t>
+          <t>post launch</t>
         </is>
       </c>
     </row>
@@ -962,12 +962,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_18,_'name':_'agency',_'label':_'agency',_'value':_'agency'}</t>
+          <t>agency</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 18, 'name': 'agency', 'label': 'Agency', 'value': 'Agency'}</t>
+          <t>Agency</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_19,_'name':_'client',_'label':_'client',_'value':_'client'}</t>
+          <t>client</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 19, 'name': 'client', 'label': 'Client', 'value': 'client'}</t>
+          <t>Client</t>
         </is>
       </c>
     </row>
@@ -996,12 +996,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_20,_'name':_'internal',_'label':_'internal',_'value':_'internal'}</t>
+          <t>internal</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 20, 'name': 'internal', 'label': 'Internal', 'value': 'internal'}</t>
+          <t>Internal</t>
         </is>
       </c>
     </row>
